--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488138_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488138_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.4734</v>
+        <v>6.9596</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9577</v>
+        <v>4.7393</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5158</v>
+        <v>2.2203</v>
       </c>
       <c r="G2" t="n">
         <v>3.2566</v>
@@ -610,13 +610,13 @@
         <v>2.594</v>
       </c>
       <c r="S2" t="n">
-        <v>2.9193</v>
+        <v>1.4055</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0096</v>
+        <v>0.7912</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9098000000000001</v>
+        <v>0.6143</v>
       </c>
       <c r="V2" t="n">
         <v>0.63</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6496</v>
+        <v>5.6793</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1959</v>
+        <v>1.9793</v>
       </c>
       <c r="F3" t="n">
-        <v>3.4538</v>
+        <v>3.7</v>
       </c>
       <c r="G3" t="n">
         <v>5.8896</v>
@@ -688,13 +688,13 @@
         <v>3.7057</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6106</v>
+        <v>0.4191</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6566</v>
+        <v>0.1269</v>
       </c>
       <c r="U3" t="n">
-        <v>0.046</v>
+        <v>0.2922</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6294</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.1478</v>
+        <v>5.2513</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3561</v>
+        <v>2.1395</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7917</v>
+        <v>3.1118</v>
       </c>
       <c r="G4" t="n">
         <v>2.0384</v>
@@ -766,13 +766,13 @@
         <v>4.0763</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7255</v>
+        <v>0.378</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8207</v>
+        <v>-0.0373</v>
       </c>
       <c r="U4" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.4153</v>
       </c>
       <c r="V4" t="n">
         <v>-0.315</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.1077</v>
+        <v>3.7712</v>
       </c>
       <c r="E5" t="n">
-        <v>3.7537</v>
+        <v>3.3188</v>
       </c>
       <c r="F5" t="n">
-        <v>0.354</v>
+        <v>0.4524</v>
       </c>
       <c r="G5" t="n">
         <v>2.5877</v>
@@ -844,13 +844,13 @@
         <v>0.9264</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5755</v>
+        <v>0.2391</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8891</v>
+        <v>0.4542</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3136</v>
+        <v>-0.2151</v>
       </c>
       <c r="V5" t="n">
         <v>0.9444</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. MENDEZ CARRION</t>
+          <t>J. PAREDES BERMEJO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.9107</v>
+        <v>3.4873</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6446</v>
+        <v>-0.9046</v>
       </c>
       <c r="F6" t="n">
-        <v>3.2662</v>
+        <v>4.3919</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2769</v>
+        <v>0.7037</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7717</v>
+        <v>1.0556</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4948</v>
+        <v>-0.3519</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3054</v>
+        <v>-0.0277</v>
       </c>
       <c r="K6" t="n">
-        <v>1.8848</v>
+        <v>0.5623</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5793</v>
+        <v>-0.59</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0285</v>
+        <v>0.7314000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1131</v>
+        <v>0.4933</v>
       </c>
       <c r="O6" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.2381</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1117</v>
+        <v>1.8529</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R6" t="n">
-        <v>2.9646</v>
+        <v>2.7793</v>
       </c>
       <c r="S6" t="n">
-        <v>2.1516</v>
+        <v>-0.0137</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1926</v>
+        <v>-0.2649</v>
       </c>
       <c r="U6" t="n">
-        <v>0.959</v>
+        <v>0.2512</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6294</v>
+        <v>0.9444</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.0005</v>
+        <v>0.3144</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6289</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. PAREDES BERMEJO</t>
+          <t>A. MENDEZ CARRION</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.874</v>
+        <v>3.1016</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2963</v>
+        <v>0.057</v>
       </c>
       <c r="F7" t="n">
-        <v>4.1703</v>
+        <v>3.0446</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7037</v>
+        <v>1.2769</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0556</v>
+        <v>1.7717</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3519</v>
+        <v>-0.4948</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0277</v>
+        <v>1.3054</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5623</v>
+        <v>1.8848</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.59</v>
+        <v>-0.5793</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7314000000000001</v>
+        <v>-0.0285</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4933</v>
+        <v>-0.1131</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2381</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8529</v>
+        <v>1.1117</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7793</v>
+        <v>2.9646</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.627</v>
+        <v>1.3424</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6566</v>
+        <v>0.605</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0296</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9444</v>
+        <v>-0.6294</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3144</v>
+        <v>-0.0005</v>
       </c>
       <c r="X7" t="n">
-        <v>0.63</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7902</v>
+        <v>1.9675</v>
       </c>
       <c r="E8" t="n">
-        <v>1.9421</v>
+        <v>2.0948</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1519</v>
+        <v>-0.1272</v>
       </c>
       <c r="G8" t="n">
         <v>1.8285</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0383</v>
+        <v>0.139</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0547</v>
+        <v>0.0979</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0164</v>
+        <v>0.041</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6793</v>
+        <v>0.9545</v>
       </c>
       <c r="E9" t="n">
-        <v>1.1972</v>
+        <v>1.4477</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5178</v>
+        <v>-0.4932</v>
       </c>
       <c r="G9" t="n">
         <v>0.8123</v>
@@ -1156,13 +1156,13 @@
         <v>0.7411</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2447</v>
+        <v>0.0305</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2736</v>
+        <v>-0.023</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0288</v>
+        <v>0.0535</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6294</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7808</v>
+        <v>-1.1495</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1285</v>
+        <v>-2.2265</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3478</v>
+        <v>1.0769</v>
       </c>
       <c r="G10" t="n">
         <v>2.0388</v>
@@ -1234,13 +1234,13 @@
         <v>2.0382</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4213</v>
+        <v>0.0525</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0174</v>
+        <v>-0.0805</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4039</v>
+        <v>0.133</v>
       </c>
       <c r="V10" t="n">
         <v>-1.5733</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7431</v>
+        <v>-1.4001</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1093</v>
+        <v>-2.8155</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3661</v>
+        <v>1.4154</v>
       </c>
       <c r="G11" t="n">
         <v>-0.7737000000000001</v>
@@ -1312,13 +1312,13 @@
         <v>1.4823</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5989</v>
+        <v>-0.2559</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.526</v>
+        <v>-0.2322</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.0236</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.7959</v>
+        <v>-1.7965</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5178</v>
+        <v>-2.4199</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7219</v>
+        <v>0.6234</v>
       </c>
       <c r="G12" t="n">
         <v>-0.8374</v>
@@ -1390,13 +1390,13 @@
         <v>0.1853</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2174</v>
+        <v>-0.2179</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3071</v>
+        <v>-0.2092</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0898</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.6531</v>
+        <v>-3.8927</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.9116</v>
+        <v>-5.0528</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2585</v>
+        <v>1.16</v>
       </c>
       <c r="G13" t="n">
         <v>-2.6766</v>
@@ -1468,13 +1468,13 @@
         <v>1.6676</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1532</v>
+        <v>-0.0864</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1816</v>
+        <v>0.0404</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0284</v>
+        <v>-0.1269</v>
       </c>
       <c r="V13" t="n">
         <v>-0.9444</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>22.6598</v>
+        <v>22.9335</v>
       </c>
       <c r="E14" t="n">
-        <v>2.083800000000002</v>
+        <v>2.3571</v>
       </c>
       <c r="F14" t="n">
-        <v>20.5764</v>
+        <v>20.5763</v>
       </c>
       <c r="G14" t="n">
         <v>16.1448</v>
@@ -1546,10 +1546,10 @@
         <v>23.1608</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1585</v>
+        <v>3.4322</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9949999999999999</v>
+        <v>1.2685</v>
       </c>
       <c r="U14" t="n">
         <v>2.1636</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3773</v>
+        <v>1.8115</v>
       </c>
       <c r="E15" t="n">
-        <v>0.353</v>
+        <v>0.255</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0243</v>
+        <v>1.5565</v>
       </c>
       <c r="G15" t="n">
         <v>0.0027</v>
@@ -1624,13 +1624,13 @@
         <v>2.7793</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3571</v>
+        <v>-0.2086</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3867</v>
+        <v>-0.4846</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7439</v>
+        <v>0.276</v>
       </c>
       <c r="V15" t="n">
         <v>2.2027</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6257</v>
+        <v>1.2957</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1369</v>
+        <v>0.5286</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4888</v>
+        <v>0.7671</v>
       </c>
       <c r="G16" t="n">
         <v>-1.3087</v>
@@ -1702,13 +1702,13 @@
         <v>1.297</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6215000000000001</v>
+        <v>0.0485</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6019</v>
+        <v>-0.2101</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0197</v>
+        <v>0.2586</v>
       </c>
       <c r="V16" t="n">
         <v>1.2589</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2548</v>
+        <v>-0.0143</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6627</v>
+        <v>1.3689</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.4079</v>
+        <v>-1.3832</v>
       </c>
       <c r="G17" t="n">
         <v>-0.7074</v>
@@ -1780,13 +1780,13 @@
         <v>0.3706</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0383</v>
+        <v>-0.3075</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2699</v>
+        <v>-0.0239</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3082</v>
+        <v>-0.2835</v>
       </c>
       <c r="V17" t="n">
         <v>0.63</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. NAVARRO GARRIDO</t>
+          <t>P. CORREA GALLARDO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4963</v>
+        <v>-0.2826</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8974</v>
+        <v>-0.6167</v>
       </c>
       <c r="F18" t="n">
-        <v>0.401</v>
+        <v>0.3341</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.1157</v>
+        <v>-1.1772</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.7194</v>
+        <v>-0.3046</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3962</v>
+        <v>-0.8725000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.1354</v>
+        <v>-1.1569</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.1769</v>
+        <v>0.1074</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0415</v>
+        <v>-1.2643</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9802999999999999</v>
+        <v>-0.0203</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5426</v>
+        <v>-0.412</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4377</v>
+        <v>0.3917</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1117</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1117</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S18" t="n">
-        <v>1.1376</v>
+        <v>-0.2907</v>
       </c>
       <c r="T18" t="n">
-        <v>0.868</v>
+        <v>-0.0892</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2696</v>
+        <v>-0.2015</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.63</v>
+        <v>0.6294</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.63</v>
+        <v>0.6294</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. CORREA GALLARDO</t>
+          <t>S. NAVARRO GARRIDO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7808</v>
+        <v>-0.7821</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9105</v>
+        <v>-1.2891</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1297</v>
+        <v>0.507</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1772</v>
+        <v>-2.1157</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3046</v>
+        <v>-1.7194</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8725000000000001</v>
+        <v>-0.3962</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.1569</v>
+        <v>-1.1354</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1074</v>
+        <v>-1.1769</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.2643</v>
+        <v>0.0415</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0203</v>
+        <v>-0.9802999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.412</v>
+        <v>-0.5426</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3917</v>
+        <v>-0.4377</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.1117</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.1117</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7889</v>
+        <v>0.8518</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.383</v>
+        <v>0.4763</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4059</v>
+        <v>0.3755</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6294</v>
+        <v>-0.63</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6294</v>
+        <v>-0.63</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2539</v>
+        <v>-1.4904</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4459</v>
+        <v>-1.8376</v>
       </c>
       <c r="F20" t="n">
-        <v>0.192</v>
+        <v>0.3472</v>
       </c>
       <c r="G20" t="n">
         <v>1.5776</v>
@@ -2014,13 +2014,13 @@
         <v>1.6676</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7451</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7039</v>
+        <v>0.3121</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0413</v>
+        <v>0.1965</v>
       </c>
       <c r="V20" t="n">
         <v>0.3144</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4538</v>
+        <v>-1.6267</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7496</v>
+        <v>-1.6516</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2958</v>
+        <v>0.0249</v>
       </c>
       <c r="G21" t="n">
         <v>-1.9307</v>
@@ -2092,13 +2092,13 @@
         <v>1.6676</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0507</v>
+        <v>-0.1222</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6019</v>
+        <v>-0.5039</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6526</v>
+        <v>0.3818</v>
       </c>
       <c r="V21" t="n">
         <v>-0.315</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5376</v>
+        <v>-1.8051</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5799</v>
+        <v>-1.1674</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9577</v>
+        <v>-0.6375999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>-2.3063</v>
@@ -2170,13 +2170,13 @@
         <v>2.7793</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1398</v>
+        <v>-0.4073</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4303</v>
+        <v>-0.1573</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.57</v>
+        <v>-0.25</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9444</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8272</v>
+        <v>-2.2809</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.338</v>
+        <v>-0.8484</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4892</v>
+        <v>-1.4325</v>
       </c>
       <c r="G23" t="n">
         <v>-0.8231000000000001</v>
@@ -2248,13 +2248,13 @@
         <v>1.1117</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0602</v>
+        <v>-0.5139</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7113</v>
+        <v>-0.2216</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.349</v>
+        <v>-0.2922</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9439</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.7324</v>
+        <v>-3.6837</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.7864</v>
+        <v>-4.6885</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0541</v>
+        <v>1.0048</v>
       </c>
       <c r="G24" t="n">
         <v>-1.2894</v>
@@ -2326,13 +2326,13 @@
         <v>1.4823</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3487</v>
+        <v>-0.3</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6019</v>
+        <v>-0.5039</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2532</v>
+        <v>0.2039</v>
       </c>
       <c r="V24" t="n">
         <v>0.3144</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.4586</v>
+        <v>-5.0658</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.7825</v>
+        <v>-3.5867</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.6761</v>
+        <v>-1.4791</v>
       </c>
       <c r="G25" t="n">
         <v>-3.0906</v>
@@ -2404,13 +2404,13 @@
         <v>1.297</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.3298</v>
+        <v>-0.9370000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6019</v>
+        <v>-0.406</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.728</v>
+        <v>-0.531</v>
       </c>
       <c r="V25" t="n">
         <v>0.6294</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-8.3772</v>
+        <v>-8.0829</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.2388</v>
+        <v>-7.0429</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.1385</v>
+        <v>-1.04</v>
       </c>
       <c r="G26" t="n">
         <v>-2.9763</v>
@@ -2482,13 +2482,13 @@
         <v>1.4823</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.1219</v>
+        <v>-0.8276</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5471</v>
+        <v>-0.3513</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.5748</v>
+        <v>-0.4763</v>
       </c>
       <c r="V26" t="n">
         <v>-0.9439</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-22.66</v>
+        <v>-22.0073</v>
       </c>
       <c r="E27" t="n">
         <v>-20.5764</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.083699999999999</v>
+        <v>-1.4308</v>
       </c>
       <c r="G27" t="n">
         <v>-16.1451</v>
@@ -2536,7 +2536,7 @@
         <v>-0.5995000000000006</v>
       </c>
       <c r="K27" t="n">
-        <v>1.552</v>
+        <v>1.551999999999999</v>
       </c>
       <c r="L27" t="n">
         <v>-2.1516</v>
@@ -2560,13 +2560,13 @@
         <v>17.6023</v>
       </c>
       <c r="S27" t="n">
-        <v>-3.158600000000001</v>
+        <v>-2.5059</v>
       </c>
       <c r="T27" t="n">
-        <v>-2.1636</v>
+        <v>-2.1634</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.9949999999999999</v>
+        <v>-0.3422000000000001</v>
       </c>
       <c r="V27" t="n">
         <v>2.202</v>
